--- a/Categoría/MDC_Categoría.xlsx
+++ b/Categoría/MDC_Categoría.xlsx
@@ -901,7 +901,7 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>111.9662756872717</v>
+        <v>111.9662756872718</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>6</v>
@@ -1003,7 +1003,7 @@
         <v>1.852</v>
       </c>
       <c r="C12" s="2">
-        <v>109.3949106905778</v>
+        <v>109.3949106905779</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>6</v>
@@ -2845,7 +2845,7 @@
         <v>6</v>
       </c>
       <c r="E120" s="2">
-        <v>3.521363659438118</v>
+        <v>3.521363659438119</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2904,7 +2904,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>8.680000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="C124" s="2">
         <v>115.8607545804091</v>
@@ -2930,7 +2930,7 @@
         <v>6</v>
       </c>
       <c r="E125" s="2">
-        <v>5.949120799917259</v>
+        <v>5.949120799917258</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3151,7 +3151,7 @@
         <v>6</v>
       </c>
       <c r="E138" s="2">
-        <v>1.775790094676437</v>
+        <v>1.775790094676438</v>
       </c>
     </row>
     <row r="139" spans="1:5">
